--- a/MetaSkillTreeTable_局外技能树表.xlsx
+++ b/MetaSkillTreeTable_局外技能树表.xlsx
@@ -2,8 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="1" r:id="R25e7bfd4a6984e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果映射" sheetId="2" r:id="Re2b907d23248410f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="1" r:id="Rd1aa50f00505469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果映射" sheetId="2" r:id="R1c6fe35a6d2b4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="板块" sheetId="3" r:id="R0da1ce2a2aad494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文案" sheetId="4" r:id="R0c878a82eb9f43d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,8 +26,18 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -35,6 +47,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF403728"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -50,7 +67,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -64,6 +81,24 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -291,6 +326,12 @@
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -322,107 +363,179 @@
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
-      <x:c r="A3" s="2" t="str">
+      <x:c r="A3" s="8" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>板块</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>板块内顺序</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="str">
+      <x:c r="D3" s="8" t="str">
         <x:v>名称key</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>前置节点</x:v>
       </x:c>
-      <x:c r="F3" s="2" t="str">
+      <x:c r="F3" s="8" t="str">
         <x:v>消耗类型</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="str">
+      <x:c r="G3" s="8" t="str">
         <x:v>消耗数量</x:v>
       </x:c>
-      <x:c r="H3" s="2" t="str">
+      <x:c r="H3" s="8" t="str">
         <x:v>是否启用</x:v>
       </x:c>
+      <x:c r="I3" s="9" t="str">
+        <x:v>说明key</x:v>
+      </x:c>
+      <x:c r="J3" s="9" t="str">
+        <x:v>图标key</x:v>
+      </x:c>
+      <x:c r="K3" s="9" t="str">
+        <x:v>布局横坐标</x:v>
+      </x:c>
+      <x:c r="L3" s="9" t="str">
+        <x:v>布局纵坐标</x:v>
+      </x:c>
+      <x:c r="M3" s="9" t="str">
+        <x:v>节点样式</x:v>
+      </x:c>
+      <x:c r="N3" s="9" t="str">
+        <x:v>分支key</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Index</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="9" t="str">
         <x:v>Board</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="9" t="str">
         <x:v>OrderInBoard</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>NameKey</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="9" t="str">
         <x:v>PrereqNodeId</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="9" t="str">
         <x:v>CostType</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
+      <x:c r="G4" s="9" t="str">
         <x:v>CostValue</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="str">
+      <x:c r="H4" s="9" t="str">
         <x:v>Enable</x:v>
       </x:c>
+      <x:c r="I4" s="9" t="str">
+        <x:v>DescriptionKey</x:v>
+      </x:c>
+      <x:c r="J4" s="9" t="str">
+        <x:v>IconKey</x:v>
+      </x:c>
+      <x:c r="K4" s="9" t="str">
+        <x:v>LayoutX</x:v>
+      </x:c>
+      <x:c r="L4" s="9" t="str">
+        <x:v>LayoutY</x:v>
+      </x:c>
+      <x:c r="M4" s="9" t="str">
+        <x:v>NodeKind</x:v>
+      </x:c>
+      <x:c r="N4" s="9" t="str">
+        <x:v>BranchKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="1" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="H5" s="1" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="I5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="K5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="L5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="M5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="N5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="1" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="str">
+      <x:c r="C6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="str">
+      <x:c r="E6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="str">
+      <x:c r="F6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="str">
+      <x:c r="G6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="H6" s="1" t="str">
+      <x:c r="H6" s="9" t="str">
         <x:v>bool</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="J6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="K6" s="9" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="L6" s="9" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M6" s="9" t="str">
+        <x:v>uint</x:v>
+      </x:c>
+      <x:c r="N6" s="9" t="str">
+        <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -450,6 +563,22 @@
       <x:c r="H7" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I7" t="str">
+        <x:v>ft_101_desc</x:v>
+      </x:c>
+      <x:c r="J7" t="str"/>
+      <x:c r="K7" t="n">
+        <x:v>-420</x:v>
+      </x:c>
+      <x:c r="L7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>ft_branch_1_0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" t="n">
@@ -476,6 +605,22 @@
       <x:c r="H8" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I8" t="str">
+        <x:v>ft_102_desc</x:v>
+      </x:c>
+      <x:c r="J8" t="str"/>
+      <x:c r="K8" t="n">
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>ft_branch_1_0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" t="n">
@@ -502,317 +647,1365 @@
       <x:c r="H9" s="4" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I9" t="str">
+        <x:v>ft_103_desc</x:v>
+      </x:c>
+      <x:c r="J9" t="str"/>
+      <x:c r="K9" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>ft_branch_1_0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" t="n">
-        <x:v>201</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>ft_201_name</x:v>
+        <x:v>ft_104_name</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>0</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H10" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>ft_104_desc</x:v>
+      </x:c>
+      <x:c r="J10" t="str"/>
+      <x:c r="K10" t="n">
+        <x:v>-230</x:v>
+      </x:c>
+      <x:c r="L10" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>ft_branch_1_1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" t="n">
-        <x:v>202</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>ft_105_name</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>ft_202_name</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="G11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>ft_105_desc</x:v>
+      </x:c>
+      <x:c r="J11" t="str"/>
+      <x:c r="K11" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H11" s="4" t="b">
-        <x:v>1</x:v>
+      <x:c r="L11" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>ft_branch_1_1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" t="n">
-        <x:v>203</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B12" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C12" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>ft_203_name</x:v>
+        <x:v>ft_106_name</x:v>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>202</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>40</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H12" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>ft_106_desc</x:v>
+      </x:c>
+      <x:c r="J12" t="str"/>
+      <x:c r="K12" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L12" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>ft_branch_1_2</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" t="n">
-        <x:v>301</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>ft_107_name</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>ft_301_name</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="G13" t="n">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H13" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>ft_107_desc</x:v>
+      </x:c>
+      <x:c r="J13" t="str"/>
+      <x:c r="K13" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L13" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>ft_branch_1_2</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" t="n">
-        <x:v>302</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B14" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>ft_302_name</x:v>
+        <x:v>ft_201_name</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>301</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>180</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H14" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>ft_201_desc</x:v>
+      </x:c>
+      <x:c r="J14" t="str"/>
+      <x:c r="K14" t="n">
+        <x:v>-420</x:v>
+      </x:c>
+      <x:c r="L14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>ft_branch_2_0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" t="n">
-        <x:v>303</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>ft_303_name</x:v>
+        <x:v>ft_202_name</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>302</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>10</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H15" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>ft_202_desc</x:v>
+      </x:c>
+      <x:c r="J15" t="str"/>
+      <x:c r="K15" t="n">
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>ft_branch_2_0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" t="n">
-        <x:v>401</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B16" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C16" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>ft_401_name</x:v>
+        <x:v>ft_203_name</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>0</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>200</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>ft_203_desc</x:v>
+      </x:c>
+      <x:c r="J16" t="str"/>
+      <x:c r="K16" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>ft_branch_2_0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" t="n">
-        <x:v>402</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C17" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="D17" t="str">
-        <x:v>ft_402_name</x:v>
+        <x:v>ft_204_name</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>401</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H17" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>ft_204_desc</x:v>
+      </x:c>
+      <x:c r="J17" t="str"/>
+      <x:c r="K17" t="n">
+        <x:v>-230</x:v>
+      </x:c>
+      <x:c r="L17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>ft_branch_2_1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" t="n">
-        <x:v>403</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B18" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>ft_403_name</x:v>
+        <x:v>ft_205_name</x:v>
       </x:c>
       <x:c r="E18" t="n">
-        <x:v>402</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H18" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>ft_205_desc</x:v>
+      </x:c>
+      <x:c r="J18" t="str"/>
+      <x:c r="K18" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>ft_branch_2_1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" t="n">
-        <x:v>501</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B19" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C19" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>ft_501_name</x:v>
+        <x:v>ft_206_name</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>0</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>220</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H19" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>ft_206_desc</x:v>
+      </x:c>
+      <x:c r="J19" t="str"/>
+      <x:c r="K19" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L19" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>ft_branch_2_2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" t="n">
-        <x:v>502</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B20" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C20" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>ft_502_name</x:v>
+        <x:v>ft_207_name</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>501</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F20" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H20" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>ft_207_desc</x:v>
+      </x:c>
+      <x:c r="J20" t="str"/>
+      <x:c r="K20" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L20" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>ft_branch_2_2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>ft_301_name</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>ft_301_desc</x:v>
+      </x:c>
+      <x:c r="J21" t="str"/>
+      <x:c r="K21" t="n">
+        <x:v>-420</x:v>
+      </x:c>
+      <x:c r="L21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>ft_branch_3_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>ft_302_name</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>ft_302_desc</x:v>
+      </x:c>
+      <x:c r="J22" t="str"/>
+      <x:c r="K22" t="n">
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>ft_branch_3_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>ft_303_name</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>ft_303_desc</x:v>
+      </x:c>
+      <x:c r="J23" t="str"/>
+      <x:c r="K23" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>ft_branch_3_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>ft_304_name</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H24" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>ft_304_desc</x:v>
+      </x:c>
+      <x:c r="J24" t="str"/>
+      <x:c r="K24" t="n">
+        <x:v>-230</x:v>
+      </x:c>
+      <x:c r="L24" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>ft_branch_3_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>ft_305_name</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G25" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>ft_305_desc</x:v>
+      </x:c>
+      <x:c r="J25" t="str"/>
+      <x:c r="K25" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L25" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>ft_branch_3_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>ft_306_name</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H26" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>ft_306_desc</x:v>
+      </x:c>
+      <x:c r="J26" t="str"/>
+      <x:c r="K26" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L26" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>ft_branch_3_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>ft_307_name</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H27" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>ft_307_desc</x:v>
+      </x:c>
+      <x:c r="J27" t="str"/>
+      <x:c r="K27" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L27" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>ft_branch_3_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>ft_401_name</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H28" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>ft_401_desc</x:v>
+      </x:c>
+      <x:c r="J28" t="str"/>
+      <x:c r="K28" t="n">
+        <x:v>-420</x:v>
+      </x:c>
+      <x:c r="L28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>ft_branch_4_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>ft_402_name</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>ft_402_desc</x:v>
+      </x:c>
+      <x:c r="J29" t="str"/>
+      <x:c r="K29" t="n">
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>ft_branch_4_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>ft_403_name</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H30" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>ft_403_desc</x:v>
+      </x:c>
+      <x:c r="J30" t="str"/>
+      <x:c r="K30" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>ft_branch_4_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>ft_404_name</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H31" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>ft_404_desc</x:v>
+      </x:c>
+      <x:c r="J31" t="str"/>
+      <x:c r="K31" t="n">
+        <x:v>-230</x:v>
+      </x:c>
+      <x:c r="L31" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>ft_branch_4_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>ft_405_name</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G32" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H32" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>ft_405_desc</x:v>
+      </x:c>
+      <x:c r="J32" t="str"/>
+      <x:c r="K32" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>ft_branch_4_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>ft_406_name</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G33" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H33" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>ft_406_desc</x:v>
+      </x:c>
+      <x:c r="J33" t="str"/>
+      <x:c r="K33" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L33" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>ft_branch_4_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>ft_407_name</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G34" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>ft_407_desc</x:v>
+      </x:c>
+      <x:c r="J34" t="str"/>
+      <x:c r="K34" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L34" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>ft_branch_4_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>ft_501_name</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H35" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>ft_501_desc</x:v>
+      </x:c>
+      <x:c r="J35" t="str"/>
+      <x:c r="K35" t="n">
+        <x:v>-420</x:v>
+      </x:c>
+      <x:c r="L35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>ft_branch_5_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>ft_502_name</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H36" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>ft_502_desc</x:v>
+      </x:c>
+      <x:c r="J36" t="str"/>
+      <x:c r="K36" t="n">
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>ft_branch_5_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="B21" t="n">
+      <x:c r="B37" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C21" t="n">
+      <x:c r="C37" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="D37" t="str">
         <x:v>ft_503_name</x:v>
       </x:c>
-      <x:c r="E21" t="n">
+      <x:c r="E37" t="n">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="F21" t="n">
+      <x:c r="F37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G21" t="n">
+      <x:c r="G37" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="H21" s="4" t="b">
-        <x:v>1</x:v>
+      <x:c r="H37" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>ft_503_desc</x:v>
+      </x:c>
+      <x:c r="J37" t="str"/>
+      <x:c r="K37" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>ft_branch_5_0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>ft_504_name</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H38" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>ft_504_desc</x:v>
+      </x:c>
+      <x:c r="J38" t="str"/>
+      <x:c r="K38" t="n">
+        <x:v>-230</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>ft_branch_5_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>ft_505_name</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H39" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>ft_505_desc</x:v>
+      </x:c>
+      <x:c r="J39" t="str"/>
+      <x:c r="K39" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>ft_branch_5_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>ft_506_name</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H40" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>ft_506_desc</x:v>
+      </x:c>
+      <x:c r="J40" t="str"/>
+      <x:c r="K40" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>ft_branch_5_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>ft_507_name</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H41" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>ft_507_desc</x:v>
+      </x:c>
+      <x:c r="J41" t="str"/>
+      <x:c r="K41" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>-210</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>ft_branch_5_2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -854,70 +2047,70 @@
       <x:c r="E2" s="1"/>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
-      <x:c r="A3" s="2" t="str">
+      <x:c r="A3" s="8" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>节点ID</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>效果ID</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="str">
+      <x:c r="D3" s="8" t="str">
         <x:v>权重</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>是否启用</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Index</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="9" t="str">
         <x:v>NodeId</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="9" t="str">
         <x:v>EffectId</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="9" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="9" t="str">
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="1" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="1" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="str">
+      <x:c r="B6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="str">
+      <x:c r="C6" s="9" t="str">
         <x:v>uint</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="str">
+      <x:c r="D6" s="9" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="str">
+      <x:c r="E6" s="9" t="str">
         <x:v>bool</x:v>
       </x:c>
     </x:row>
@@ -1174,6 +2367,1978 @@
       </x:c>
       <x:c r="E21" s="4" t="b">
         <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E40" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" s="4" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>类名</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>FamilyTreeBoard</x:v>
+      </x:c>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
+      <x:c r="E1" s="10"/>
+      <x:c r="F1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="10" t="str">
+        <x:v>是否读取</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>IsConfig</x:v>
+      </x:c>
+      <x:c r="C2" s="10"/>
+      <x:c r="D2" s="10"/>
+      <x:c r="E2" s="10"/>
+      <x:c r="F2" s="10"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>名称key</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>说明key</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>图标key</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
+        <x:v>显示顺序</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str">
+        <x:v>是否启用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="9" t="str">
+        <x:v>Index</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>NameKey</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>DescriptionKey</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>IconKey</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str">
+        <x:v>Order</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26" customHeight="1">
+      <x:c r="A6" s="9" t="str">
+        <x:v>uint</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>uint</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>ft_board_1_name</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>ft_board_1_desc</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str"/>
+      <x:c r="E7" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>ft_board_2_name</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>ft_board_2_desc</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str"/>
+      <x:c r="E8" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>ft_board_3_name</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>ft_board_3_desc</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str"/>
+      <x:c r="E9" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>ft_board_4_name</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>ft_board_4_desc</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str"/>
+      <x:c r="E10" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26" customHeight="1">
+      <x:c r="A11" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>ft_board_5_name</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>ft_board_5_desc</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str"/>
+      <x:c r="E11" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="64" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>类名</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>FamilyTreeText</x:v>
+      </x:c>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="10"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="10" t="str">
+        <x:v>是否读取</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>IsConfig</x:v>
+      </x:c>
+      <x:c r="C2" s="10"/>
+      <x:c r="D2" s="10"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="9" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>文案key</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>简体中文</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>英文回退</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="9" t="str">
+        <x:v>Index</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>Key</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>ChineseSimplified</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>English</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26" customHeight="1">
+      <x:c r="A5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26" customHeight="1">
+      <x:c r="A6" s="9" t="str">
+        <x:v>uint</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>ft_101_name</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>乡里声望</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>Local standing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>ft_101_desc</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>乡邻熟悉往来路线，为远行队伍筹措随行物资。</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>ft_102_name</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>乡邻协助</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>Community support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>ft_102_desc</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>熟悉乡里物资去向，扩大归途能够带回的收获。</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26" customHeight="1">
+      <x:c r="A11" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>ft_103_name</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>远行筹备</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>Expedition planning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26" customHeight="1">
+      <x:c r="A12" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>ft_103_desc</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>提前整理人员与物资，使远征收获更易带回。</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>ft_201_name</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>田事营建</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>Field construction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26" customHeight="1">
+      <x:c r="A14" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>ft_201_desc</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>积累农田营建经验，减少田间设施的施工时间。</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="26" customHeight="1">
+      <x:c r="A15" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>ft_202_name</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>仓储规整</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>Warehouse order</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>ft_202_desc</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>分类整理家族仓储，为更多种类的物品腾出位置。</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>ft_203_name</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>精耕务农</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>Careful cultivation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>ft_203_desc</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>改进田间劳作方法，增加实际工作周期的收获。</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26" customHeight="1">
+      <x:c r="A19" s="10" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>ft_301_name</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>养士强身</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>Retainer conditioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26" customHeight="1">
+      <x:c r="A20" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>ft_301_desc</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>以日常训练改善门客体魄，增进远行时的生命上限。</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>ft_302_name</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>随行整备</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>Supply organization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="10" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>ft_302_desc</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>改进归家后的物资归类，增加局外仓库可容纳的物品种类。</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="10" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>ft_303_name</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>营地补员</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="str">
+        <x:v>Camp reinforcement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="10" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>ft_303_desc</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>掌握安全营地中的整备方法，解锁扎营补充减员。</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="26" customHeight="1">
+      <x:c r="A25" s="10" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="str">
+        <x:v>ft_401_name</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>守备习武</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="str">
+        <x:v>Martial practice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="10" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>ft_401_desc</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>将日常武艺操练用于门客实战，提高普通攻击伤害。</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="10" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>ft_402_name</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>防护操练</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="str">
+        <x:v>Defensive practice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="10" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>ft_402_desc</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>学习护身与协防，减少门客受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="10" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>ft_403_name</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>后勤储备</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="str">
+        <x:v>Return logistics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="10" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>ft_403_desc</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>为远行与归途预留运载余力，提高结算带出件数。</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="10" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>ft_501_name</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>疾行练习</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="str">
+        <x:v>Marching drills</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="26" customHeight="1">
+      <x:c r="A32" s="10" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="str">
+        <x:v>ft_501_desc</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>熟悉负重行路，提高派遣角色的水平移动速度。</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="26" customHeight="1">
+      <x:c r="A33" s="10" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="str">
+        <x:v>ft_502_name</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>行囊收整</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="str">
+        <x:v>Pack organization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="26" customHeight="1">
+      <x:c r="A34" s="10" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B34" s="10" t="str">
+        <x:v>ft_502_desc</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>将归来物资分门别类，为局外仓库存放腾出位置。</x:v>
+      </x:c>
+      <x:c r="D34" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="26" customHeight="1">
+      <x:c r="A35" s="10" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B35" s="10" t="str">
+        <x:v>ft_503_name</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>远征整备</x:v>
+      </x:c>
+      <x:c r="D35" s="10" t="str">
+        <x:v>Expedition readiness</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="26" customHeight="1">
+      <x:c r="A36" s="10" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B36" s="10" t="str">
+        <x:v>ft_503_desc</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
+        <x:v>完善长途远行的物资准备，提高结算带出件数。</x:v>
+      </x:c>
+      <x:c r="D36" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="26" customHeight="1">
+      <x:c r="A37" s="10" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B37" s="10" t="str">
+        <x:v>ft_104_name</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>乡里互助</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="str">
+        <x:v>Shared storage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="26" customHeight="1">
+      <x:c r="A38" s="10" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B38" s="10" t="str">
+        <x:v>ft_104_desc</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>利用互助经验整理储藏位置，增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="26" customHeight="1">
+      <x:c r="A39" s="10" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B39" s="10" t="str">
+        <x:v>ft_105_name</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>物资归整</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="str">
+        <x:v>Stock organization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="26" customHeight="1">
+      <x:c r="A40" s="10" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B40" s="10" t="str">
+        <x:v>ft_105_desc</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>改进货物分类与入库次序，进一步增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="26" customHeight="1">
+      <x:c r="A41" s="10" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B41" s="10" t="str">
+        <x:v>ft_106_name</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>工役协调</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="str">
+        <x:v>Coordinated works</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="26" customHeight="1">
+      <x:c r="A42" s="10" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B42" s="10" t="str">
+        <x:v>ft_106_desc</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>协调材料生产建筑的施工步骤，缩短新建和升级时间。</x:v>
+      </x:c>
+      <x:c r="D42" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="26" customHeight="1">
+      <x:c r="A43" s="10" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B43" s="10" t="str">
+        <x:v>ft_107_name</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>匠作联络</x:v>
+      </x:c>
+      <x:c r="D43" s="10" t="str">
+        <x:v>Artisan ties</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="26" customHeight="1">
+      <x:c r="A44" s="10" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B44" s="10" t="str">
+        <x:v>ft_107_desc</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>借助工匠间的经验往来，缩短图纸生产建筑的施工时间。</x:v>
+      </x:c>
+      <x:c r="D44" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="26" customHeight="1">
+      <x:c r="A45" s="10" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B45" s="10" t="str">
+        <x:v>ft_204_name</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>材场规制</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="str">
+        <x:v>Material workflow</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="26" customHeight="1">
+      <x:c r="A46" s="10" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>ft_204_desc</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>整理材料生产的作业步骤，增加每个实际工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="D46" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="26" customHeight="1">
+      <x:c r="A47" s="10" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>ft_205_name</x:v>
+      </x:c>
+      <x:c r="C47" s="10" t="str">
+        <x:v>工坊熟作</x:v>
+      </x:c>
+      <x:c r="D47" s="10" t="str">
+        <x:v>Workshop practice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="26" customHeight="1">
+      <x:c r="A48" s="10" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B48" s="10" t="str">
+        <x:v>ft_205_desc</x:v>
+      </x:c>
+      <x:c r="C48" s="10" t="str">
+        <x:v>积累工坊经验，增加图纸生产建筑每个工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="D48" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="26" customHeight="1">
+      <x:c r="A49" s="10" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B49" s="10" t="str">
+        <x:v>ft_206_name</x:v>
+      </x:c>
+      <x:c r="C49" s="10" t="str">
+        <x:v>市业周转</x:v>
+      </x:c>
+      <x:c r="D49" s="10" t="str">
+        <x:v>Trade workflow</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="26" customHeight="1">
+      <x:c r="A50" s="10" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B50" s="10" t="str">
+        <x:v>ft_206_desc</x:v>
+      </x:c>
+      <x:c r="C50" s="10" t="str">
+        <x:v>优化经营作业流程，增加钱财生产建筑每个工作周期的产出。</x:v>
+      </x:c>
+      <x:c r="D50" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="26" customHeight="1">
+      <x:c r="A51" s="10" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B51" s="10" t="str">
+        <x:v>ft_207_name</x:v>
+      </x:c>
+      <x:c r="C51" s="10" t="str">
+        <x:v>田事精作</x:v>
+      </x:c>
+      <x:c r="D51" s="10" t="str">
+        <x:v>Improved fieldwork</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="26" customHeight="1">
+      <x:c r="A52" s="10" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B52" s="10" t="str">
+        <x:v>ft_207_desc</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="str">
+        <x:v>将生产整备经验用于农田，进一步增加每个工作周期的收获。</x:v>
+      </x:c>
+      <x:c r="D52" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="26" customHeight="1">
+      <x:c r="A53" s="10" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B53" s="10" t="str">
+        <x:v>ft_304_name</x:v>
+      </x:c>
+      <x:c r="C53" s="10" t="str">
+        <x:v>起居调养</x:v>
+      </x:c>
+      <x:c r="D53" s="10" t="str">
+        <x:v>Daily conditioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="26" customHeight="1">
+      <x:c r="A54" s="10" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B54" s="10" t="str">
+        <x:v>ft_304_desc</x:v>
+      </x:c>
+      <x:c r="C54" s="10" t="str">
+        <x:v>改善远行前的调养，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="D54" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="26" customHeight="1">
+      <x:c r="A55" s="10" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B55" s="10" t="str">
+        <x:v>ft_305_name</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="str">
+        <x:v>体魄训练</x:v>
+      </x:c>
+      <x:c r="D55" s="10" t="str">
+        <x:v>Physical training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="26" customHeight="1">
+      <x:c r="A56" s="10" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B56" s="10" t="str">
+        <x:v>ft_305_desc</x:v>
+      </x:c>
+      <x:c r="C56" s="10" t="str">
+        <x:v>持续锻炼体魄，进一步提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="D56" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="26" customHeight="1">
+      <x:c r="A57" s="10" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B57" s="10" t="str">
+        <x:v>ft_306_name</x:v>
+      </x:c>
+      <x:c r="C57" s="10" t="str">
+        <x:v>护行训练</x:v>
+      </x:c>
+      <x:c r="D57" s="10" t="str">
+        <x:v>Travel defense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="26" customHeight="1">
+      <x:c r="A58" s="10" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B58" s="10" t="str">
+        <x:v>ft_306_desc</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>练习行路中的防护动作，减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="26" customHeight="1">
+      <x:c r="A59" s="10" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B59" s="10" t="str">
+        <x:v>ft_307_name</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>携行整备</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>Returning supplies</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="26" customHeight="1">
+      <x:c r="A60" s="10" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B60" s="10" t="str">
+        <x:v>ft_307_desc</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>归纳门客带回物资的存放方式，增加局外仓库格位。</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="26" customHeight="1">
+      <x:c r="A61" s="10" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B61" s="10" t="str">
+        <x:v>ft_404_name</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>守备操练</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>Guard drills</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="26" customHeight="1">
+      <x:c r="A62" s="10" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B62" s="10" t="str">
+        <x:v>ft_404_desc</x:v>
+      </x:c>
+      <x:c r="C62" s="10" t="str">
+        <x:v>加强基础攻防练习，提高派遣角色普通攻击伤害。</x:v>
+      </x:c>
+      <x:c r="D62" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="26" customHeight="1">
+      <x:c r="A63" s="10" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B63" s="10" t="str">
+        <x:v>ft_405_name</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="str">
+        <x:v>协防规程</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="str">
+        <x:v>Defensive coordination</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="26" customHeight="1">
+      <x:c r="A64" s="10" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B64" s="10" t="str">
+        <x:v>ft_405_desc</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="str">
+        <x:v>统一协防动作，进一步减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="D64" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="26" customHeight="1">
+      <x:c r="A65" s="10" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B65" s="10" t="str">
+        <x:v>ft_406_name</x:v>
+      </x:c>
+      <x:c r="C65" s="10" t="str">
+        <x:v>固守准备</x:v>
+      </x:c>
+      <x:c r="D65" s="10" t="str">
+        <x:v>Defensive readiness</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="26" customHeight="1">
+      <x:c r="A66" s="10" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B66" s="10" t="str">
+        <x:v>ft_406_desc</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="str">
+        <x:v>改善守备人员的体魄准备，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="26" customHeight="1">
+      <x:c r="A67" s="10" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B67" s="10" t="str">
+        <x:v>ft_407_name</x:v>
+      </x:c>
+      <x:c r="C67" s="10" t="str">
+        <x:v>轮值整备</x:v>
+      </x:c>
+      <x:c r="D67" s="10" t="str">
+        <x:v>Duty conditioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="26" customHeight="1">
+      <x:c r="A68" s="10" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B68" s="10" t="str">
+        <x:v>ft_407_desc</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="str">
+        <x:v>以轮值调养改善远行状态，进一步提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="26" customHeight="1">
+      <x:c r="A69" s="10" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B69" s="10" t="str">
+        <x:v>ft_504_name</x:v>
+      </x:c>
+      <x:c r="C69" s="10" t="str">
+        <x:v>轻装行进</x:v>
+      </x:c>
+      <x:c r="D69" s="10" t="str">
+        <x:v>Light-footed travel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="26" customHeight="1">
+      <x:c r="A70" s="10" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B70" s="10" t="str">
+        <x:v>ft_504_desc</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="str">
+        <x:v>练习行装分配，提高派遣角色水平移动速度。</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="26" customHeight="1">
+      <x:c r="A71" s="10" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B71" s="10" t="str">
+        <x:v>ft_505_name</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>山路适应</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>Trail conditioning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="26" customHeight="1">
+      <x:c r="A72" s="10" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B72" s="10" t="str">
+        <x:v>ft_505_desc</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="str">
+        <x:v>通过山路行走锻炼，提高派遣角色生命上限。</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="26" customHeight="1">
+      <x:c r="A73" s="10" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B73" s="10" t="str">
+        <x:v>ft_506_name</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
+        <x:v>临阵配合</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="str">
+        <x:v>Field coordination</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="26" customHeight="1">
+      <x:c r="A74" s="10" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="str">
+        <x:v>ft_506_desc</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>练习行动中的攻击配合，提高派遣角色普通攻击伤害。</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="26" customHeight="1">
+      <x:c r="A75" s="10" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="str">
+        <x:v>ft_507_name</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>防护整备</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>Field protection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="26" customHeight="1">
+      <x:c r="A76" s="10" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B76" s="10" t="str">
+        <x:v>ft_507_desc</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>整理远行防护经验，减少派遣角色受到的普通伤害。</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>Permanent family development. See the effect preview below.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="26" customHeight="1">
+      <x:c r="A77" s="10" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B77" s="10" t="str">
+        <x:v>ft_board_1_name</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>影响力</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>Influence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="26" customHeight="1">
+      <x:c r="A78" s="10" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B78" s="10" t="str">
+        <x:v>ft_board_1_desc</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>积累乡里联系与物资组织能力。</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>Influence improvements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="26" customHeight="1">
+      <x:c r="A79" s="10" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B79" s="10" t="str">
+        <x:v>ft_branch_1_0</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="str">
+        <x:v>远行筹备</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="26" customHeight="1">
+      <x:c r="A80" s="10" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B80" s="10" t="str">
+        <x:v>ft_branch_1_1</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>仓储互助</x:v>
+      </x:c>
+      <x:c r="D80" s="10" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="26" customHeight="1">
+      <x:c r="A81" s="10" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B81" s="10" t="str">
+        <x:v>ft_branch_1_2</x:v>
+      </x:c>
+      <x:c r="C81" s="10" t="str">
+        <x:v>工役协作</x:v>
+      </x:c>
+      <x:c r="D81" s="10" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="26" customHeight="1">
+      <x:c r="A82" s="10" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B82" s="10" t="str">
+        <x:v>ft_board_2_name</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="str">
+        <x:v>家族产业</x:v>
+      </x:c>
+      <x:c r="D82" s="10" t="str">
+        <x:v>Family industry</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="26" customHeight="1">
+      <x:c r="A83" s="10" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B83" s="10" t="str">
+        <x:v>ft_board_2_desc</x:v>
+      </x:c>
+      <x:c r="C83" s="10" t="str">
+        <x:v>改善营建与工作生产，让经营积累反哺远行。</x:v>
+      </x:c>
+      <x:c r="D83" s="10" t="str">
+        <x:v>Family industry improvements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="26" customHeight="1">
+      <x:c r="A84" s="10" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B84" s="10" t="str">
+        <x:v>ft_branch_2_0</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="str">
+        <x:v>田事经营</x:v>
+      </x:c>
+      <x:c r="D84" s="10" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="26" customHeight="1">
+      <x:c r="A85" s="10" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B85" s="10" t="str">
+        <x:v>ft_branch_2_1</x:v>
+      </x:c>
+      <x:c r="C85" s="10" t="str">
+        <x:v>工坊生产</x:v>
+      </x:c>
+      <x:c r="D85" s="10" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="26" customHeight="1">
+      <x:c r="A86" s="10" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B86" s="10" t="str">
+        <x:v>ft_branch_2_2</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="str">
+        <x:v>产业整备</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="26" customHeight="1">
+      <x:c r="A87" s="10" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B87" s="10" t="str">
+        <x:v>ft_board_3_name</x:v>
+      </x:c>
+      <x:c r="C87" s="10" t="str">
+        <x:v>门客培养</x:v>
+      </x:c>
+      <x:c r="D87" s="10" t="str">
+        <x:v>Retainer training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="26" customHeight="1">
+      <x:c r="A88" s="10" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B88" s="10" t="str">
+        <x:v>ft_board_3_desc</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="str">
+        <x:v>以调养与训练改善派遣队伍的长期准备。</x:v>
+      </x:c>
+      <x:c r="D88" s="10" t="str">
+        <x:v>Retainer training improvements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="26" customHeight="1">
+      <x:c r="A89" s="10" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B89" s="10" t="str">
+        <x:v>ft_branch_3_0</x:v>
+      </x:c>
+      <x:c r="C89" s="10" t="str">
+        <x:v>养士整备</x:v>
+      </x:c>
+      <x:c r="D89" s="10" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="26" customHeight="1">
+      <x:c r="A90" s="10" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B90" s="10" t="str">
+        <x:v>ft_branch_3_1</x:v>
+      </x:c>
+      <x:c r="C90" s="10" t="str">
+        <x:v>体魄培养</x:v>
+      </x:c>
+      <x:c r="D90" s="10" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="26" customHeight="1">
+      <x:c r="A91" s="10" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B91" s="10" t="str">
+        <x:v>ft_branch_3_2</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="str">
+        <x:v>护行准备</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="26" customHeight="1">
+      <x:c r="A92" s="10" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B92" s="10" t="str">
+        <x:v>ft_board_4_name</x:v>
+      </x:c>
+      <x:c r="C92" s="10" t="str">
+        <x:v>局外战斗</x:v>
+      </x:c>
+      <x:c r="D92" s="10" t="str">
+        <x:v>Defensive training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="26" customHeight="1">
+      <x:c r="A93" s="10" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B93" s="10" t="str">
+        <x:v>ft_board_4_desc</x:v>
+      </x:c>
+      <x:c r="C93" s="10" t="str">
+        <x:v>以守备训练改善派遣门客的通用攻防准备。</x:v>
+      </x:c>
+      <x:c r="D93" s="10" t="str">
+        <x:v>Defensive training improvements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="26" customHeight="1">
+      <x:c r="A94" s="10" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B94" s="10" t="str">
+        <x:v>ft_branch_4_0</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="str">
+        <x:v>守备基础</x:v>
+      </x:c>
+      <x:c r="D94" s="10" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="26" customHeight="1">
+      <x:c r="A95" s="10" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B95" s="10" t="str">
+        <x:v>ft_branch_4_1</x:v>
+      </x:c>
+      <x:c r="C95" s="10" t="str">
+        <x:v>武艺协防</x:v>
+      </x:c>
+      <x:c r="D95" s="10" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="26" customHeight="1">
+      <x:c r="A96" s="10" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B96" s="10" t="str">
+        <x:v>ft_branch_4_2</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="str">
+        <x:v>固守调养</x:v>
+      </x:c>
+      <x:c r="D96" s="10" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="26" customHeight="1">
+      <x:c r="A97" s="10" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B97" s="10" t="str">
+        <x:v>ft_board_5_name</x:v>
+      </x:c>
+      <x:c r="C97" s="10" t="str">
+        <x:v>局内战斗</x:v>
+      </x:c>
+      <x:c r="D97" s="10" t="str">
+        <x:v>Expedition combat</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="26" customHeight="1">
+      <x:c r="A98" s="10" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B98" s="10" t="str">
+        <x:v>ft_board_5_desc</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="str">
+        <x:v>改善远行队伍的行动、携行与临阵配合。</x:v>
+      </x:c>
+      <x:c r="D98" s="10" t="str">
+        <x:v>Expedition combat improvements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="26" customHeight="1">
+      <x:c r="A99" s="10" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B99" s="10" t="str">
+        <x:v>ft_branch_5_0</x:v>
+      </x:c>
+      <x:c r="C99" s="10" t="str">
+        <x:v>远征基础</x:v>
+      </x:c>
+      <x:c r="D99" s="10" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="26" customHeight="1">
+      <x:c r="A100" s="10" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B100" s="10" t="str">
+        <x:v>ft_branch_5_1</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="str">
+        <x:v>山路行进</x:v>
+      </x:c>
+      <x:c r="D100" s="10" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="26" customHeight="1">
+      <x:c r="A101" s="10" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B101" s="10" t="str">
+        <x:v>ft_branch_5_2</x:v>
+      </x:c>
+      <x:c r="C101" s="10" t="str">
+        <x:v>临阵整备</x:v>
+      </x:c>
+      <x:c r="D101" s="10" t="str">
+        <x:v>Preparation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
